--- a/artfynd/A 56351-2019 artfynd.xlsx
+++ b/artfynd/A 56351-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56351-2019 artfynd.xlsx
+++ b/artfynd/A 56351-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,715 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126559695</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56953</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>450785</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6225227</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126560201</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95487</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>450916</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6225445</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Britta Lidberg, Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126559794</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57939</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>450766</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6225328</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126559793</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>450739</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6225312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126560071</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80637</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>450915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6225445</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126559795</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57939</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>450902</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6225127</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126560070</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80637</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bivaröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>450938</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6225451</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Knislinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Britta Lidberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56351-2019 artfynd.xlsx
+++ b/artfynd/A 56351-2019 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>126560201</v>
       </c>
       <c r="B4" t="n">
-        <v>95487</v>
+        <v>95562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>126560071</v>
       </c>
       <c r="B7" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>126560070</v>
       </c>
       <c r="B9" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
